--- a/hk.xlsx
+++ b/hk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LEI XIAO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2471766-7AB0-484F-9F78-4B5AE916C972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E50358-547F-42B3-BF82-D7EC65D6A508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33254,7 +33254,7 @@
         <v>973</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>958</v>
+        <v>69</v>
       </c>
       <c r="E315" s="1" t="s">
         <v>974</v>
@@ -33449,7 +33449,7 @@
       </c>
       <c r="C328" s="1"/>
       <c r="D328" s="1" t="s">
-        <v>880</v>
+        <v>21</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>55</v>
@@ -34021,7 +34021,7 @@
       </c>
       <c r="C366" s="1"/>
       <c r="D366" s="1" t="s">
-        <v>21</v>
+        <v>958</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>136</v>
@@ -34668,7 +34668,7 @@
       </c>
       <c r="C409" s="1"/>
       <c r="D409" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>54</v>
@@ -36913,7 +36913,7 @@
       </c>
       <c r="C558" s="1"/>
       <c r="D558" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>1569</v>
@@ -37035,7 +37035,7 @@
       </c>
       <c r="C566" s="1"/>
       <c r="D566" s="1" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>189</v>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="C656" s="1"/>
       <c r="D656" s="1" t="s">
-        <v>54</v>
+        <v>325</v>
       </c>
       <c r="E656" s="1" t="s">
         <v>1805</v>
@@ -38492,7 +38492,7 @@
       </c>
       <c r="C663" s="1"/>
       <c r="D663" s="1" t="s">
-        <v>838</v>
+        <v>16</v>
       </c>
       <c r="E663" s="1" t="s">
         <v>1820</v>
@@ -40433,7 +40433,7 @@
       </c>
       <c r="C792" s="1"/>
       <c r="D792" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E792" s="1" t="s">
         <v>2136</v>
@@ -40988,7 +40988,7 @@
       </c>
       <c r="C829" s="1"/>
       <c r="D829" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E829" s="1" t="s">
         <v>1657</v>
@@ -41110,7 +41110,7 @@
       </c>
       <c r="C837" s="1"/>
       <c r="D837" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E837" s="1" t="s">
         <v>32</v>
@@ -43263,7 +43263,7 @@
       </c>
       <c r="C980" s="1"/>
       <c r="D980" s="1" t="s">
-        <v>319</v>
+        <v>2493</v>
       </c>
       <c r="E980" s="1" t="s">
         <v>163</v>
@@ -45108,7 +45108,7 @@
       </c>
       <c r="C1103" s="1"/>
       <c r="D1103" s="1" t="s">
-        <v>872</v>
+        <v>16</v>
       </c>
       <c r="E1103" s="1" t="s">
         <v>370</v>
@@ -45753,7 +45753,7 @@
       </c>
       <c r="C1146" s="1"/>
       <c r="D1146" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E1146" s="1" t="s">
         <v>3072</v>
@@ -45783,7 +45783,7 @@
       </c>
       <c r="C1148" s="1"/>
       <c r="D1148" s="1" t="s">
-        <v>880</v>
+        <v>21</v>
       </c>
       <c r="E1148" s="1" t="s">
         <v>3077</v>
@@ -47599,7 +47599,7 @@
       </c>
       <c r="C1268" s="1"/>
       <c r="D1268" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E1268" s="1" t="s">
         <v>1096</v>
@@ -47800,7 +47800,7 @@
       </c>
       <c r="C1281" s="1"/>
       <c r="D1281" s="1" t="s">
-        <v>343</v>
+        <v>741</v>
       </c>
       <c r="E1281" s="1" t="s">
         <v>177</v>
@@ -50293,7 +50293,7 @@
       </c>
       <c r="C1446" s="1"/>
       <c r="D1446" s="1" t="s">
-        <v>958</v>
+        <v>69</v>
       </c>
       <c r="E1446" s="1" t="s">
         <v>3810</v>
@@ -54189,7 +54189,7 @@
       </c>
       <c r="C1704" s="1"/>
       <c r="D1704" s="1" t="s">
-        <v>872</v>
+        <v>16</v>
       </c>
       <c r="E1704" s="1" t="s">
         <v>4442</v>
@@ -55039,7 +55039,7 @@
       </c>
       <c r="C1760" s="1"/>
       <c r="D1760" s="1" t="s">
-        <v>1712</v>
+        <v>838</v>
       </c>
       <c r="E1760" s="1" t="s">
         <v>750</v>
@@ -55114,7 +55114,7 @@
       </c>
       <c r="C1765" s="1"/>
       <c r="D1765" s="1" t="s">
-        <v>829</v>
+        <v>1597</v>
       </c>
       <c r="E1765" s="1" t="s">
         <v>4587</v>
@@ -56005,7 +56005,7 @@
         <v>4726</v>
       </c>
       <c r="D1824" s="1" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E1824" s="1" t="s">
         <v>337</v>
@@ -59009,7 +59009,7 @@
       </c>
       <c r="C2024" s="1"/>
       <c r="D2024" s="1" t="s">
-        <v>16</v>
+        <v>880</v>
       </c>
       <c r="E2024" s="1" t="s">
         <v>5198</v>
@@ -59744,7 +59744,7 @@
       </c>
       <c r="C2073" s="1"/>
       <c r="D2073" s="1" t="s">
-        <v>38</v>
+        <v>880</v>
       </c>
       <c r="E2073" s="1" t="s">
         <v>3856</v>
@@ -61941,7 +61941,7 @@
       </c>
       <c r="C2218" s="1"/>
       <c r="D2218" s="1" t="s">
-        <v>21</v>
+        <v>958</v>
       </c>
       <c r="E2218" s="1" t="s">
         <v>5659</v>
@@ -64287,7 +64287,7 @@
       </c>
       <c r="C2374" s="1"/>
       <c r="D2374" s="1" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E2374" s="1" t="s">
         <v>6041</v>
@@ -67764,7 +67764,7 @@
       </c>
       <c r="C2605" s="1"/>
       <c r="D2605" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E2605" s="1" t="s">
         <v>6603</v>
@@ -68231,7 +68231,7 @@
       </c>
       <c r="C2636" s="1"/>
       <c r="D2636" s="1" t="s">
-        <v>872</v>
+        <v>16</v>
       </c>
       <c r="E2636" s="1" t="s">
         <v>6675</v>
@@ -68674,7 +68674,7 @@
       </c>
       <c r="C2665" s="1"/>
       <c r="D2665" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="E2665" s="1" t="s">
         <v>355</v>
@@ -69036,7 +69036,7 @@
       </c>
       <c r="C2689" s="1"/>
       <c r="D2689" s="1" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="E2689" s="1" t="s">
         <v>3454</v>
@@ -69066,7 +69066,7 @@
       </c>
       <c r="C2691" s="1"/>
       <c r="D2691" s="1" t="s">
-        <v>880</v>
+        <v>21</v>
       </c>
       <c r="E2691" s="1" t="s">
         <v>6811</v>
@@ -69263,7 +69263,7 @@
       </c>
       <c r="C2704" s="1"/>
       <c r="D2704" s="1" t="s">
-        <v>16</v>
+        <v>958</v>
       </c>
       <c r="E2704" s="1" t="s">
         <v>880</v>
@@ -71343,7 +71343,7 @@
       </c>
       <c r="C2842" s="1"/>
       <c r="D2842" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E2842" s="1" t="s">
         <v>2249</v>
@@ -71388,7 +71388,7 @@
       </c>
       <c r="C2845" s="1"/>
       <c r="D2845" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E2845" s="1" t="s">
         <v>805</v>
@@ -72039,7 +72039,7 @@
       </c>
       <c r="C2888" s="1"/>
       <c r="D2888" s="1" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="E2888" s="1" t="s">
         <v>7266</v>
@@ -75240,7 +75240,7 @@
       </c>
       <c r="C3101" s="1"/>
       <c r="D3101" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E3101" s="1" t="s">
         <v>4511</v>
@@ -75765,7 +75765,7 @@
       </c>
       <c r="C3136" s="1"/>
       <c r="D3136" s="1" t="s">
-        <v>958</v>
+        <v>69</v>
       </c>
       <c r="E3136" s="1" t="s">
         <v>7872</v>
@@ -75855,7 +75855,7 @@
       </c>
       <c r="C3142" s="1"/>
       <c r="D3142" s="1" t="s">
-        <v>343</v>
+        <v>1256</v>
       </c>
       <c r="E3142" s="1" t="s">
         <v>256</v>
@@ -79118,7 +79118,7 @@
       </c>
       <c r="C3359" s="1"/>
       <c r="D3359" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="E3359" s="1" t="s">
         <v>8408</v>
@@ -80455,7 +80455,7 @@
       </c>
       <c r="C3448" s="1"/>
       <c r="D3448" s="1" t="s">
-        <v>319</v>
+        <v>2493</v>
       </c>
       <c r="E3448" s="1" t="s">
         <v>8633</v>
@@ -81104,7 +81104,7 @@
       </c>
       <c r="C3491" s="1"/>
       <c r="D3491" s="1" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="E3491" s="1" t="s">
         <v>376</v>
@@ -82147,7 +82147,7 @@
         <v>8899</v>
       </c>
       <c r="D3560" s="1" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E3560" s="1" t="s">
         <v>8900</v>
@@ -84238,7 +84238,7 @@
       </c>
       <c r="C3699" s="1"/>
       <c r="D3699" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E3699" s="1" t="s">
         <v>256</v>
@@ -84268,7 +84268,7 @@
       </c>
       <c r="C3701" s="1"/>
       <c r="D3701" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E3701" s="1" t="s">
         <v>9233</v>
@@ -84328,7 +84328,7 @@
       </c>
       <c r="C3705" s="1"/>
       <c r="D3705" s="1" t="s">
-        <v>16</v>
+        <v>880</v>
       </c>
       <c r="E3705" s="1" t="s">
         <v>9244</v>
